--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/customers.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/customers.xlsx
@@ -413,21 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.6</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.4</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
@@ -438,14 +473,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
@@ -456,14 +512,35 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
@@ -474,14 +551,35 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Charlie</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
@@ -492,14 +590,35 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Diana</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
@@ -510,14 +629,35 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -528,14 +668,35 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Fiona</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/customers.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/customers.xlsx
@@ -413,56 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.6</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.5</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.4</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.3</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.2</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.1</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
@@ -473,35 +438,14 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
@@ -512,35 +456,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
@@ -551,35 +474,14 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Charlie</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
@@ -590,35 +492,14 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Diana</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
@@ -629,35 +510,14 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -668,35 +528,14 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Fiona</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/customers.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/customers.xlsx
@@ -413,21 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.4</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
@@ -438,14 +468,32 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
@@ -456,14 +504,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
@@ -474,14 +540,32 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Charlie</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
@@ -492,14 +576,32 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Diana</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
@@ -510,14 +612,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -528,14 +648,32 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Fiona</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
